--- a/out/LSTM-mamba2_repeat_3_000006.xlsx
+++ b/out/LSTM-mamba2_repeat_3_000006.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.7867500136927617</v>
+        <v>-0.3</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.7867500136927617</v>
+        <v>-0.3</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.7867500136927617</v>
+        <v>-0.3</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.7867500136927617</v>
+        <v>-0.3</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.7867500136927617</v>
+        <v>-0.3</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.7867500136927617</v>
+        <v>-0.3</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.7867500136927617</v>
+        <v>-0.3</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0001903103879385162</v>
+        <v>-6.556325642217417e-05</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2449442937428258</v>
+        <v>0.08438480768506497</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.7867500136927617</v>
+        <v>-0.3</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.4903521399144605</v>
+        <v>0.1689297339021736</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.05656770542692913</v>
+        <v>-0.0194880177913958</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.7867500136927617</v>
+        <v>-0.3</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.1881862779279579</v>
+        <v>0.06483122663724702</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.7867500136927617</v>
+        <v>-0.3</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.1881862779279579</v>
+        <v>0.06483122663724702</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.7867500136927617</v>
+        <v>-0.3</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.18798868051649</v>
+        <v>0.06475166442322568</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.6070618200184978</v>
+        <v>0.2444321660704994</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.7867500136927617</v>
+        <v>-0.3</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.403321447708949</v>
+        <v>0.5541030433219986</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.1161544390982094</v>
+        <v>0.0467694028973443</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.7867500136927617</v>
+        <v>-0.3</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.027682417318861</v>
+        <v>0.4028526571241431</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.2034555159456009</v>
+        <v>0.08192082715885056</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.7867500136927617</v>
+        <v>-0.3</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.318496259471515</v>
+        <v>0.5199482700256048</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1114198826612208</v>
+        <v>0.04486282609988666</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.7867500136927617</v>
+        <v>-0.3</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.337704707038412</v>
+        <v>0.527682525776231</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.04601803417885431</v>
+        <v>0.01852900052948198</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.7867500136927617</v>
+        <v>-0.3</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.318204089966035</v>
+        <v>0.5198305874830726</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.05733403116514607</v>
+        <v>0.02308603502812542</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.7867500136927617</v>
+        <v>-0.3</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.38686282369472</v>
+        <v>0.5474763734630048</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.03452249273389506</v>
+        <v>0.01389973439154032</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.7867500136927617</v>
+        <v>-0.3</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.398535071816853</v>
+        <v>0.5521757733858368</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.02624727311725166</v>
+        <v>0.01056623891274916</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.7867500136927617</v>
+        <v>-0.3</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.416491191744301</v>
+        <v>0.5594043808195763</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01160795712306236</v>
+        <v>0.004670697256883739</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.7867500136927617</v>
+        <v>-0.3</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.413437963348807</v>
+        <v>0.5581718723189736</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.00920863975381595</v>
+        <v>0.003705173577296268</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.420246464710818</v>
+        <v>0.5609111095432001</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.004565204441058321</v>
+        <v>0.001836089473792515</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.7867500136927617</v>
+        <v>-0.3</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.420159897904276</v>
+        <v>0.5608732506654687</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.002651100280759771</v>
+        <v>0.001065585874391671</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.42089739116167</v>
+        <v>0.561167360520143</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001324504740752701</v>
+        <v>0.0005302929371958355</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.420890735838519</v>
+        <v>0.5611616940443013</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0006504197810230281</v>
+        <v>0.0002594676309391166</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.420869109951017</v>
+        <v>0.5611499993118744</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.000375492416680912</v>
+        <v>0.0001485320277835259</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.420969793786597</v>
+        <v>0.5611874566156971</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001222222964963988</v>
+        <v>4.633531262135388e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.42083732742832</v>
+        <v>0.5611314695106868</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>6.012794327086025e-05</v>
+        <v>1.970370261998147e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.420833048083354</v>
+        <v>0.5611267567002347</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>2.924674582151908e-05</v>
+        <v>9.677176780651038e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.420833823888034</v>
+        <v>0.5611241460540584</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.159126312874283e-05</v>
+        <v>2.110541340889784e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.420827661461012</v>
+        <v>0.5611186804883393</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>6.636802982518164e-06</v>
+        <v>-2.090799254370459e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.420826964315608</v>
+        <v>0.5611152958698885</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>1.549918929005845e-07</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.42082062945506</v>
+        <v>0.5611096284396148</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.420816386844906</v>
+        <v>0.5611100089746726</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.420816615165941</v>
+        <v>0.5611102372957072</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.7867500136927617</v>
+        <v>-0.3</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.420816705110591</v>
+        <v>0.5611103272403571</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.420815847177006</v>
+        <v>0.5611094693067723</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.420816075498041</v>
+        <v>0.561109697627807</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.42081527983383</v>
+        <v>0.5611089019635953</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.420815342103202</v>
+        <v>0.5611089642329684</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.42081536977848</v>
+        <v>0.5611089919082453</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.420815521992502</v>
+        <v>0.5611091441222685</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.420815176051541</v>
+        <v>0.5611087981813068</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.420815252158552</v>
+        <v>0.5611088742883185</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.7867500136927617</v>
+        <v>-0.3</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.420815418210214</v>
+        <v>0.56110904033998</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.7867500136927617</v>
+        <v>-0.3</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.420815777988814</v>
+        <v>0.5611094001185801</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.7867500136927617</v>
+        <v>-0.3</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.420815798745272</v>
+        <v>0.5611094208750378</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.7867500136927617</v>
+        <v>-0.3</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.42081590252756</v>
+        <v>0.5611095246573263</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.7867500136927617</v>
+        <v>-0.3</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.420816130848595</v>
+        <v>0.561109752978361</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.420816006309849</v>
+        <v>0.5611096284396148</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.420816033985126</v>
+        <v>0.5611096561148916</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.7867500136927617</v>
+        <v>-0.3</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.42081608933568</v>
+        <v>0.5611097114654455</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.7867500136927617</v>
+        <v>-0.3</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.42081635225081</v>
+        <v>0.5611099743805763</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.42081626922498</v>
+        <v>0.5611098913547455</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.420816061660402</v>
+        <v>0.5611096837901687</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.420816075498041</v>
+        <v>0.561109697627807</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.420816213874426</v>
+        <v>0.5611098360041917</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.420815930202837</v>
+        <v>0.5611095523326032</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.420815757232356</v>
+        <v>0.5611093793621224</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.7867500136927617</v>
+        <v>-0.3</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.420815653450068</v>
+        <v>0.5611092755798339</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.420815798745272</v>
+        <v>0.5611094208750378</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.420816040903945</v>
+        <v>0.561109663033711</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.420815867933464</v>
+        <v>0.5611094900632301</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.420815570424237</v>
+        <v>0.561109192554003</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.420815556586599</v>
+        <v>0.5611091787163646</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.420815189889179</v>
+        <v>0.5611088120189454</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.420815189889179</v>
+        <v>0.5611088120189454</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.420815127619806</v>
+        <v>0.5611087497495723</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.7867500136927617</v>
+        <v>-0.3</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.420815023837517</v>
+        <v>0.5611086459672837</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.7867500136927617</v>
+        <v>-0.3</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.420814850867037</v>
+        <v>0.561108472996803</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.7867500136927617</v>
+        <v>-0.3</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.420814899298771</v>
+        <v>0.5611085214285375</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.7867500136927617</v>
+        <v>-0.3</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.420814539520171</v>
+        <v>0.5611081616499375</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.420814498007256</v>
+        <v>0.5611081201370222</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.7867500136927617</v>
+        <v>-0.3</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.42081455335781</v>
+        <v>0.5611081754875759</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.420814608708364</v>
+        <v>0.5611082308381298</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.420814650221279</v>
+        <v>0.5611082723510452</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.420814380387329</v>
+        <v>0.561108002517095</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.420814435737883</v>
+        <v>0.5611080578676491</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.420814581033087</v>
+        <v>0.5611082031628529</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.420814546438991</v>
+        <v>0.5611081685687567</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.420814532601352</v>
+        <v>0.5611081547311181</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.420814622546002</v>
+        <v>0.5611082446757683</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.420814940811687</v>
+        <v>0.5611085629414529</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.420814760922387</v>
+        <v>0.5611083830521528</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.420814802435302</v>
+        <v>0.5611084245650683</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.3</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.420814615627183</v>
+        <v>0.561108237756949</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.420814684815375</v>
+        <v>0.5611083069451414</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.420814484169618</v>
+        <v>0.5611081062993836</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.420814525682533</v>
+        <v>0.561108147812299</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.3</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.42081455335781</v>
+        <v>0.5611081754875759</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-mamba2_repeat_3_000006.xlsx
+++ b/out/LSTM-mamba2_repeat_3_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.7867500136927617</v>
+        <v>0.7052000093893224</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.7867500136927617</v>
+        <v>0.7052000093893224</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893224</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.386750013692762</v>
+        <v>0.2445617031931147</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.4160766030030931</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.6160766030030932</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.7867500136927617</v>
+        <v>0.04456170319311462</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.386750013692762</v>
+        <v>0.04456170319311462</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.4160766030030931</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.6160766030030932</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.386750013692762</v>
+        <v>0.2445617031931147</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893224</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.386750013692762</v>
+        <v>0.2445617031931147</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.4160766030030931</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.503542575915647</v>
+        <v>-1.076714909199301</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.6160766030030932</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.7867500136927617</v>
+        <v>-0.6160766030030932</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-2.103542575915647</v>
+        <v>0.2445617031931146</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.386750013692762</v>
+        <v>0.2445617031931146</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893224</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893224</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893224</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.386750013692762</v>
+        <v>0.2445617031931146</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.4160766030030932</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.6160766030030934</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.7867500136927617</v>
+        <v>0.04456170319311445</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.7867500136927617</v>
+        <v>0.7052000093893224</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893224</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893224</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893224</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893224</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893224</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893224</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893224</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.7867500136927617</v>
+        <v>0.9052000093893224</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0001903103879385162</v>
+        <v>-0.0002039071873849025</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2449442937428258</v>
+        <v>0.2624442233076423</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.7867500136927617</v>
+        <v>0.7052000093893224</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.4903521399144605</v>
+        <v>0.5253855392132387</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.05656770542692913</v>
+        <v>-0.06060925567581215</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.7867500136927617</v>
+        <v>0.7052000093893224</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.1881862779279579</v>
+        <v>0.2016310604444453</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.7867500136927617</v>
+        <v>0.7052000093893224</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.1881862779279579</v>
+        <v>0.2016310604444453</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.7867500136927617</v>
+        <v>0.7052000093893224</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.18798868051649</v>
+        <v>0.2014394852660326</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.6070618200184978</v>
+        <v>0.5885602176483616</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.7867500136927617</v>
+        <v>0.7052000093893224</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.403321447708949</v>
+        <v>1.379732206703559</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.1161544390982094</v>
+        <v>0.1126144280510729</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.7867500136927617</v>
+        <v>0.7052000093893224</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.027682417318861</v>
+        <v>1.015541631691052</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.2034555159456009</v>
+        <v>0.1972548508686569</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.7867500136927617</v>
+        <v>0.7052000093893224</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.318496259471515</v>
+        <v>1.297492108103897</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1114198826612208</v>
+        <v>0.108023696295216</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.7867500136927617</v>
+        <v>0.7052000093893224</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.337704707038412</v>
+        <v>1.316115105023956</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.04601803417885431</v>
+        <v>0.04461555656139751</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.7867500136927617</v>
+        <v>0.7052000093893224</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.318204089966035</v>
+        <v>1.297208802321123</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.05733403116514607</v>
+        <v>0.05558715482639893</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.7867500136927617</v>
+        <v>0.7052000093893224</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.38686282369472</v>
+        <v>1.363775043933932</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.03452249273389506</v>
+        <v>0.03347005693734049</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.7867500136927617</v>
+        <v>0.7052000093893224</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.398535071816853</v>
+        <v>1.37509146373631</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.02624727311725166</v>
+        <v>0.0254462409692912</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.7867500136927617</v>
+        <v>0.7052000093893224</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.416491191744301</v>
+        <v>1.392500202347686</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01160795712306236</v>
+        <v>0.01125354499244201</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.7867500136927617</v>
+        <v>0.04456170319311455</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.413437963348807</v>
+        <v>1.38953979429677</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.00920863975381595</v>
+        <v>0.008928674242544784</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-2.103542575915647</v>
+        <v>0.0445617031931145</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.420246464710818</v>
+        <v>1.396141289096318</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.004565204441058321</v>
+        <v>0.004425121546313238</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.7867500136927617</v>
+        <v>-0.6160766030030933</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.420159897904276</v>
+        <v>1.396057201665319</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.002651100280759771</v>
+        <v>0.002572551860627773</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.6160766030030933</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.42089739116167</v>
+        <v>1.396772341152389</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001324504740752701</v>
+        <v>0.001283775930313887</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.420890735838519</v>
+        <v>1.396765736539356</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0006504197810230281</v>
+        <v>0.0006302972438863562</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.420869109951017</v>
+        <v>1.39674462003367</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.000375492416680912</v>
+        <v>0.0003654794583472038</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.420969793786597</v>
+        <v>1.396842071353764</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001222222964963988</v>
+        <v>0.0001177583562684549</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.42083732742832</v>
+        <v>1.396714038656793</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>6.012794327086025e-05</v>
+        <v>5.788215212358921e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.420833048083354</v>
+        <v>1.396709734461653</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.6160766030030934</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.420833823888034</v>
+        <v>1.396710309620575</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.386750013692762</v>
+        <v>0.2445617031931145</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.420827661461012</v>
+        <v>1.396704223300564</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>6.636802982518164e-06</v>
+        <v>3.727602236888622e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893224</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.420826964315608</v>
+        <v>1.396702990109411</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.386750013692762</v>
+        <v>0.2445617031931146</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.42082062945506</v>
+        <v>1.396696655248864</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.4160766030030932</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.420816386844906</v>
+        <v>1.39669241263871</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.4160766030030933</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.420816615165941</v>
+        <v>1.396692640959745</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.7867500136927617</v>
+        <v>0.2445617031931145</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.420816705110591</v>
+        <v>1.396692730904395</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893224</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.420815847177006</v>
+        <v>1.39669187297081</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893224</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.420816075498041</v>
+        <v>1.396692101291845</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893224</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.42081527983383</v>
+        <v>1.396691305627633</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893224</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.420815342103202</v>
+        <v>1.396691367897006</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893224</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.42081536977848</v>
+        <v>1.396691395572283</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893224</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.420815521992502</v>
+        <v>1.396691547786306</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893224</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.420815176051541</v>
+        <v>1.396691201845345</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893224</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.420815252158552</v>
+        <v>1.396691277952356</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.7867500136927617</v>
+        <v>0.9052000093893224</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.420815418210214</v>
+        <v>1.396691444004018</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.7867500136927617</v>
+        <v>0.7052000093893224</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.420815777988814</v>
+        <v>1.396691803782618</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.7867500136927617</v>
+        <v>0.7052000093893224</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.420815798745272</v>
+        <v>1.396691824539076</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.7867500136927617</v>
+        <v>0.7052000093893224</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.42081590252756</v>
+        <v>1.396691928321364</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.7867500136927617</v>
+        <v>0.04456170319311445</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.420816130848595</v>
+        <v>1.396692156642399</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.6160766030030934</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.420816006309849</v>
+        <v>1.396692032103653</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.6160766030030934</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.420816033985126</v>
+        <v>1.39669205977893</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.7867500136927617</v>
+        <v>0.04456170319311445</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.42081608933568</v>
+        <v>1.396692115129483</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.7867500136927617</v>
+        <v>0.7052000093893224</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.42081635225081</v>
+        <v>1.396692378044614</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.386750013692762</v>
+        <v>0.2445617031931146</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.42081626922498</v>
+        <v>1.396692295018783</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.6160766030030933</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.420816061660402</v>
+        <v>1.396692087454206</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.420816075498041</v>
+        <v>1.396692101291845</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.420816213874426</v>
+        <v>1.39669223966823</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.420815930202837</v>
+        <v>1.396691955996641</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.6160766030030934</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.420815757232356</v>
+        <v>1.39669178302616</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.7867500136927617</v>
+        <v>0.04456170319311445</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.420815653450068</v>
+        <v>1.396691679243872</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893224</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.420815798745272</v>
+        <v>1.396691824539076</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893224</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.420816040903945</v>
+        <v>1.396692066697749</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893224</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.420815867933464</v>
+        <v>1.396691893727268</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893224</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.420815570424237</v>
+        <v>1.396691596218041</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893224</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.420815556586599</v>
+        <v>1.396691582380402</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893224</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.420815189889179</v>
+        <v>1.396691215682983</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893224</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.420815189889179</v>
+        <v>1.396691215682983</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893224</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.420815127619806</v>
+        <v>1.39669115341361</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.7867500136927617</v>
+        <v>0.9052000093893224</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.420815023837517</v>
+        <v>1.396691049631321</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.7867500136927617</v>
+        <v>0.7052000093893224</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.420814850867037</v>
+        <v>1.396690876660841</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.7867500136927617</v>
+        <v>0.7052000093893224</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.420814899298771</v>
+        <v>1.396690925092575</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.7867500136927617</v>
+        <v>0.04456170319311455</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.420814539520171</v>
+        <v>1.396690565313975</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-2.103542575915647</v>
+        <v>0.0445617031931145</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.420814498007256</v>
+        <v>1.39669052380106</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.7867500136927617</v>
+        <v>-0.6160766030030933</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.42081455335781</v>
+        <v>1.396690579151614</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.6160766030030933</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.420814608708364</v>
+        <v>1.396690634502168</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.420814650221279</v>
+        <v>1.396690676015083</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.420814380387329</v>
+        <v>1.396690406181133</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.420814435737883</v>
+        <v>1.396690461531687</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.420814581033087</v>
+        <v>1.396690606826891</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.420814546438991</v>
+        <v>1.396690572232794</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.6160766030030934</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.420814532601352</v>
+        <v>1.396690558395156</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.386750013692762</v>
+        <v>0.2445617031931145</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.420814622546002</v>
+        <v>1.396690648339806</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893224</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.420814940811687</v>
+        <v>1.396690966605491</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893224</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.420814760922387</v>
+        <v>1.396690786716191</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893224</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.420814802435302</v>
+        <v>1.396690828229106</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.386750013692762</v>
+        <v>0.2445617031931146</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.420814615627183</v>
+        <v>1.396690641420987</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.4160766030030932</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.420814684815375</v>
+        <v>1.396690710609179</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.420814484169618</v>
+        <v>1.396690509963422</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.420814525682533</v>
+        <v>1.396690551476337</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.42081455335781</v>
+        <v>1.396690579151614</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-mamba2_repeat_3_000006.xlsx
+++ b/out/LSTM-mamba2_repeat_3_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.2439365535974503</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.7052000093893224</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.139088898897171</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.7052000093893224</v>
+        <v>-0.3700000000000002</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.04545307159423828</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.9052000093893224</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.008147910237312317</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.2445617031931147</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.01318478584289551</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.4160766030030931</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.01245364546775818</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.02065075188875198</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.003437023609876633</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.6160766030030932</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.007665961980819702</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.04456170319311462</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.001109737902879715</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.04456170319311462</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.01193171739578247</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.4160766030030931</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.02193808928132057</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.009025022387504578</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.01041536778211594</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.01553607359528542</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.0193711444735527</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.01160860061645508</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.6160766030030932</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.001409951597452164</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.2445617031931147</v>
+        <v>0.16</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.01843669265508652</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.9052000093893224</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.01043280214071274</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.2445617031931147</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.0008806847035884857</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.4160766030030931</v>
+        <v>0.16</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.01603087410330772</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.076714909199301</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.01926187798380852</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.6160766030030932</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.000607714056968689</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.6160766030030932</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.003863878548145294</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.2445617031931146</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.01411502063274384</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.2445617031931146</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.06588026136159897</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.9052000093893224</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.05284164100885391</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.9052000093893224</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.02120310068130493</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.9052000093893224</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.00643593817949295</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.2445617031931146</v>
+        <v>0.16</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.008796878159046173</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.4160766030030932</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.02011352777481079</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.01547444984316826</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.6160766030030934</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.02373842149972916</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.04456170319311445</v>
+        <v>-0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.02394119650125504</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.7052000093893224</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.01636689901351929</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.9052000093893224</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.01855034381151199</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.9052000093893224</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.006518218666315079</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.9052000093893224</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.005886811763048172</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.9052000093893224</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.01665298640727997</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.9052000093893224</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.0385328084230423</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.9052000093893224</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.05852789431810379</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.9052000093893224</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.0915616899728775</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.9052000093893224</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0002039071873849025</v>
+        <v>-0.0002147892381881829</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2624442233076423</v>
+        <v>0.2764504808246421</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.09210263192653656</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.7052000093893224</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.5253855392132387</v>
+        <v>0.5534241389394077</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.06060925567581215</v>
+        <v>-0.06384377903018326</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.04819449037313461</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.7052000093893224</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2016310604444453</v>
+        <v>0.2123919125562706</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.03337895125150681</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.7052000093893224</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2016310604444453</v>
+        <v>0.2123919125562706</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.0338396430015564</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.7052000093893224</v>
+        <v>-0.16</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2014394852660326</v>
+        <v>0.2122870208674138</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.5885602176483616</v>
+        <v>0.32224995302188</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.02641773223876953</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.7052000093893224</v>
+        <v>-0.16</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.379732206703559</v>
+        <v>0.8574286018864545</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.1126144280510729</v>
+        <v>0.06165883541313678</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.04703593254089355</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.7052000093893224</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.015541631691052</v>
+        <v>0.6580261833159409</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.1972548508686569</v>
+        <v>0.1080012978322583</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.05142588913440704</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.7052000093893224</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.297492108103897</v>
+        <v>0.8124004796011378</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.108023696295216</v>
+        <v>0.05914567918649577</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.05198755115270615</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.7052000093893224</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.316115105023956</v>
+        <v>0.8225970141004305</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.04461555656139751</v>
+        <v>0.02442783004820433</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.03593851625919342</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.7052000093893224</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.297208802321123</v>
+        <v>0.8122453858993386</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.05558715482639893</v>
+        <v>0.03043547040501048</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.06041820347309113</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.7052000093893224</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.363775043933932</v>
+        <v>0.8486922032064423</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.03347005693734049</v>
+        <v>0.01832608460554905</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.04175889492034912</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.7052000093893224</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.37509146373631</v>
+        <v>0.8548882485274109</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0254462409692912</v>
+        <v>0.01393128488208621</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.05374991148710251</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.7052000093893224</v>
+        <v>-0.3</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.392500202347686</v>
+        <v>0.8644192681598223</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01125354499244201</v>
+        <v>0.006159863922315439</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.01492076367139816</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.04456170319311455</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.38953979429677</v>
+        <v>0.8627960831391411</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.008928674242544784</v>
+        <v>0.004885568705899022</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.02263308875262737</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.0445617031931145</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.396141289096318</v>
+        <v>0.8664081047888869</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.004425121546313238</v>
+        <v>0.002421435855405895</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.01793248951435089</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.6160766030030933</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.396057201665319</v>
+        <v>0.866359798931007</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.002572551860627773</v>
+        <v>0.001405962361630327</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.000260528177022934</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.6160766030030933</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.396772341152389</v>
+        <v>0.8667490062123037</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001283775930313887</v>
+        <v>0.0006990265804423489</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.0165744461119175</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.396765736539356</v>
+        <v>0.8667431296516852</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0006302972438863562</v>
+        <v>0.000342832427648186</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.01668917015194893</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.39674462003367</v>
+        <v>0.8667292900290715</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0003654794583472038</v>
+        <v>0.0001985968194520669</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.009305283427238464</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.396842071353764</v>
+        <v>0.8667805921058797</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001177583562684549</v>
+        <v>6.195910341915722e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.007244370877742767</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.396714038656793</v>
+        <v>0.8667079801752239</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>5.788215212358921e-05</v>
+        <v>2.868686720906565e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.002872660756111145</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.396709734461653</v>
+        <v>0.8667033667654663</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>2.924674582151908e-05</v>
+        <v>1.456956904086805e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.001600839197635651</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.6160766030030934</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.396710309620575</v>
+        <v>0.8667015525705642</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.159126312874283e-05</v>
+        <v>4.480721787853046e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.004927888512611389</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.2445617031931145</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.396704223300564</v>
+        <v>0.8666959318162725</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>3.727602236888622e-06</v>
+        <v>8.184014912590811e-07</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.009392373263835907</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.9052000093893224</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.396702990109411</v>
+        <v>0.8666930832435705</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>1.549918929005845e-07</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.004882227629423141</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.2445617031931146</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.396696655248864</v>
+        <v>0.8666874158132968</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-1.754611730575562e-05</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.4160766030030932</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.39669241263871</v>
+        <v>0.8666877963483546</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.008892551064491272</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.4160766030030933</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.396692640959745</v>
+        <v>0.8666880246693892</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.005501385778188705</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.2445617031931145</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.396692730904395</v>
+        <v>0.8666881146140392</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.0113009437918663</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.9052000093893224</v>
+        <v>0.16</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.39669187297081</v>
+        <v>0.8666872566804543</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.02858631312847137</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.9052000093893224</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.396692101291845</v>
+        <v>0.8666874850014891</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.03874355554580688</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.9052000093893224</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.396691305627633</v>
+        <v>0.8666866893372773</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.02237743884325027</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.9052000093893224</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.396691367897006</v>
+        <v>0.8666867516066504</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.01559869199991226</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.9052000093893224</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.396691395572283</v>
+        <v>0.8666867792819273</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.02229861915111542</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.9052000093893224</v>
+        <v>0.3</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.396691547786306</v>
+        <v>0.8666869314959506</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.01129331439733505</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.9052000093893224</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.396691201845345</v>
+        <v>0.8666865855549888</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.009707838296890259</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.9052000093893224</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.396691277952356</v>
+        <v>0.8666866616620005</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.001205705106258392</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.9052000093893224</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.396691444004018</v>
+        <v>0.866686827713662</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.01620875298976898</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.7052000093893224</v>
+        <v>-0.16</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.396691803782618</v>
+        <v>0.8666871874922621</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.02373942732810974</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.7052000093893224</v>
+        <v>-0.16</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.396691824539076</v>
+        <v>0.8666872082487198</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.02490884065628052</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.7052000093893224</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.396691928321364</v>
+        <v>0.8666873120310084</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.004541382193565369</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.04456170319311445</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.396692156642399</v>
+        <v>0.866687540352043</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.008631110191345215</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.6160766030030934</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.396692032103653</v>
+        <v>0.8666874158132968</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.01750250533223152</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.6160766030030934</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.39669205977893</v>
+        <v>0.8666874434885736</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.001220032572746277</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.04456170319311445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.396692115129483</v>
+        <v>0.8666874988391275</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.002039916813373566</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.7052000093893224</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.396692378044614</v>
+        <v>0.8666877617542583</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.002894341945648193</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.2445617031931146</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.396692295018783</v>
+        <v>0.8666876787284276</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.001794379204511642</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.6160766030030933</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.396692087454206</v>
+        <v>0.8666874711638507</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.005033385008573532</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.396692101291845</v>
+        <v>0.8666874850014891</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.004001837223768234</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.39669223966823</v>
+        <v>0.8666876233778738</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.001191496849060059</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.396691955996641</v>
+        <v>0.8666873397062852</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.001137871295213699</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.6160766030030934</v>
+        <v>0.16</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.39669178302616</v>
+        <v>0.8666871667358044</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.01545371860265732</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.04456170319311445</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.396691679243872</v>
+        <v>0.8666870629535159</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.01108724623918533</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.9052000093893224</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.396691824539076</v>
+        <v>0.8666872082487198</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.0001558884978294373</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.9052000093893224</v>
+        <v>0.16</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.396692066697749</v>
+        <v>0.866687450407393</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.004504144191741943</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.9052000093893224</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.396691893727268</v>
+        <v>0.8666872774369121</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.001123994588851929</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.9052000093893224</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.396691596218041</v>
+        <v>0.8666869799276851</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.01490036398172379</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.9052000093893224</v>
+        <v>0.3</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.396691582380402</v>
+        <v>0.8666869660900466</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.01200403273105621</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.9052000093893224</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.396691215682983</v>
+        <v>0.8666865993926274</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.01360100507736206</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.9052000093893224</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.396691215682983</v>
+        <v>0.8666865993926274</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.03344438225030899</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.9052000093893224</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.39669115341361</v>
+        <v>0.8666865371232543</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.01618385314941406</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.9052000093893224</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.396691049631321</v>
+        <v>0.8666864333409657</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.005545079708099365</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.7052000093893224</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.396690876660841</v>
+        <v>0.866686260370485</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.009486790746450424</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.7052000093893224</v>
+        <v>0.16</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.396690925092575</v>
+        <v>0.8666863088022195</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.006089434027671814</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.04456170319311455</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.396690565313975</v>
+        <v>0.8666859490236195</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.002443782985210419</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.0445617031931145</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.39669052380106</v>
+        <v>0.8666859075107042</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.004811331629753113</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6160766030030933</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.396690579151614</v>
+        <v>0.8666859628612579</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.0053272545337677</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.6160766030030933</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.396690634502168</v>
+        <v>0.8666860182118118</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.00647253543138504</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.396690676015083</v>
+        <v>0.8666860597247272</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.006444215774536133</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.396690406181133</v>
+        <v>0.866685789890777</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.005549602210521698</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.396690461531687</v>
+        <v>0.8666858452413311</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.006581190973520279</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.396690606826891</v>
+        <v>0.8666859905365349</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.007126800715923309</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.396690572232794</v>
+        <v>0.8666859559424387</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.009497411549091339</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6160766030030934</v>
+        <v>0.16</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.396690558395156</v>
+        <v>0.8666859421048001</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.01372256129980087</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.2445617031931145</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.396690648339806</v>
+        <v>0.8666860320494503</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.05085358768701553</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.9052000093893224</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.396690966605491</v>
+        <v>0.866686350315135</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.0292636901140213</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.9052000093893224</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.396690786716191</v>
+        <v>0.8666861704258348</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.01086047291755676</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.9052000093893224</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.396690828229106</v>
+        <v>0.8666862119387503</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.001916274428367615</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.2445617031931146</v>
+        <v>0.16</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.396690641420987</v>
+        <v>0.866686025130631</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.007070921361446381</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.4160766030030932</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.396690710609179</v>
+        <v>0.8666860943188234</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.002143107354640961</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.396690509963422</v>
+        <v>0.8666858936730656</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.00624808669090271</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999996</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.396690551476337</v>
+        <v>0.866685935185981</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.0009808540344238281</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999996</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.396690579151614</v>
+        <v>0.8666859628612579</v>
       </c>
     </row>
   </sheetData>
